--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1321-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1321-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31E8538E-EBA8-4D3C-95D6-8281E523BA6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6840624F-312F-46FB-A3B4-C7D6B2E0724F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{AFD1F3D1-DE52-4D0C-8339-BC8AD98FD052}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{EB42D355-A8A8-490A-A8E4-700D0CAF9233}"/>
   </bookViews>
   <sheets>
     <sheet name="1321-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1436,26 +1436,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8347F6BF-85BD-4A76-8BA9-5998D5C28410}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0507DCF0-4F3A-4893-824A-43EF33B23D2B}">
   <dimension ref="A1:X38"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="9" width="6.25" customWidth="1"/>
-    <col min="10" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1489,7 +1488,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1525,7 +1524,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1577,7 +1576,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1645,7 +1644,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2024</v>
       </c>
@@ -1717,7 +1716,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2023</v>
       </c>
@@ -1789,7 +1788,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2022</v>
       </c>
@@ -1861,7 +1860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2021</v>
       </c>
@@ -1933,7 +1932,7 @@
         <v>2.27</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2020</v>
       </c>
@@ -2005,7 +2004,7 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2019</v>
       </c>
@@ -2077,7 +2076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2018</v>
       </c>
@@ -2149,7 +2148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2017</v>
       </c>
@@ -2221,7 +2220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2016</v>
       </c>
@@ -2293,7 +2292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2015</v>
       </c>
@@ -2365,7 +2364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33">
         <v>2014</v>
       </c>
@@ -2437,7 +2436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2013</v>
       </c>
@@ -2509,7 +2508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="33">
         <v>2012</v>
       </c>
@@ -2581,7 +2580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2011</v>
       </c>
@@ -2653,7 +2652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="33">
         <v>2010</v>
       </c>
@@ -2725,7 +2724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="35">
         <v>2009</v>
       </c>
@@ -2797,7 +2796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="33">
         <v>2008</v>
       </c>
@@ -2869,7 +2868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2007</v>
       </c>
@@ -2941,7 +2940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="33">
         <v>2006</v>
       </c>
@@ -3013,7 +3012,7 @@
         <v>1.23</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="35">
         <v>2005</v>
       </c>
@@ -3085,7 +3084,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="33">
         <v>2004</v>
       </c>
@@ -3157,7 +3156,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2003</v>
       </c>
@@ -3229,7 +3228,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="33">
         <v>2002</v>
       </c>
@@ -3301,7 +3300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2001</v>
       </c>
@@ -3373,7 +3372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="33">
         <v>2000</v>
       </c>
@@ -3445,7 +3444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>1999</v>
       </c>
@@ -3517,7 +3516,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="33">
         <v>1998</v>
       </c>
@@ -3589,7 +3588,7 @@
         <v>5.36</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>1997</v>
       </c>
@@ -3661,7 +3660,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="33">
         <v>1996</v>
       </c>
@@ -3733,7 +3732,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>1995</v>
       </c>
@@ -3805,7 +3804,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="33">
         <v>1994</v>
       </c>
@@ -3877,7 +3876,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>1993</v>
       </c>
@@ -3949,7 +3948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="33">
         <v>1992</v>
       </c>
@@ -4021,7 +4020,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35" t="s">
         <v>38</v>
       </c>
